--- a/docs/Farm_Management_System_Metric_v1.xlsx
+++ b/docs/Farm_Management_System_Metric_v1.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaron\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8DE73FB-3E13-46C7-B989-6D51339F71B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D005CC03-7F26-4E12-BC7D-048484190A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="479" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="562" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Asset Management" sheetId="2" r:id="rId2"/>
     <sheet name="Paddock &amp; Crop Log" sheetId="3" r:id="rId3"/>
-    <sheet name="Harvest Inputs" sheetId="5" r:id="rId4"/>
-    <sheet name="Harvest Ledger" sheetId="4" r:id="rId5"/>
-    <sheet name="Silo Management" sheetId="6" r:id="rId6"/>
+    <sheet name="Chemical Records" sheetId="7" r:id="rId4"/>
+    <sheet name="Harvest Plan &amp; Inputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Harvest Ledger" sheetId="4" r:id="rId6"/>
+    <sheet name="Silo Management" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="147">
   <si>
     <t>Crop Type</t>
   </si>
@@ -431,6 +432,54 @@
   </si>
   <si>
     <t>Annual Maintenance</t>
+  </si>
+  <si>
+    <t>Start of 2026</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Required by</t>
+  </si>
+  <si>
+    <t>Audit - (standard delivery vessel)</t>
+  </si>
+  <si>
+    <t>Start of August</t>
+  </si>
+  <si>
+    <t>Crops to use on</t>
+  </si>
+  <si>
+    <t>Herbicide</t>
+  </si>
+  <si>
+    <t>Glyphosate</t>
+  </si>
+  <si>
+    <t>Wheat, Canola, Barley</t>
+  </si>
+  <si>
+    <t>Prothioconazole</t>
+  </si>
+  <si>
+    <t>Fungacide</t>
+  </si>
+  <si>
+    <t>Cost per Drum</t>
+  </si>
+  <si>
+    <t>Imazamox + Imazapyr</t>
+  </si>
+  <si>
+    <t>Chemical Log: Chemical per Hectare</t>
+  </si>
+  <si>
+    <t>Order?</t>
   </si>
 </sst>
 </file>
@@ -564,7 +613,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -579,10 +628,6 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -594,23 +639,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -927,15 +973,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -1097,21 +1143,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1138,10 +1184,10 @@
       <c r="H3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="14" t="s">
         <v>130</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -1155,10 +1201,10 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="15" t="s">
         <v>124</v>
       </c>
       <c r="C4" s="5">
@@ -1180,10 +1226,10 @@
       <c r="H4" s="10">
         <v>500</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="29">
         <v>1200</v>
       </c>
-      <c r="J4" s="34"/>
+      <c r="J4" s="29"/>
       <c r="K4" s="5">
         <f>G4/H4</f>
         <v>29.333333333333332</v>
@@ -1222,10 +1268,10 @@
       <c r="H5" s="10">
         <v>300</v>
       </c>
-      <c r="I5" s="34">
+      <c r="I5" s="29">
         <v>1200</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="29">
         <v>20000</v>
       </c>
       <c r="K5" s="5">
@@ -1266,10 +1312,10 @@
       <c r="H6" s="10">
         <v>400</v>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="29">
         <v>1200</v>
       </c>
-      <c r="J6" s="34"/>
+      <c r="J6" s="29"/>
       <c r="K6" s="5">
         <f>G6/H6</f>
         <v>54.166666666666671</v>
@@ -1283,38 +1329,38 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="29">
         <v>5000</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="29">
         <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="29">
         <v>1200</v>
       </c>
-      <c r="J9" s="35"/>
+      <c r="J9" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1332,7 +1378,7 @@
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="51" customWidth="1"/>
+    <col min="8" max="8" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="21" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
@@ -1345,26 +1391,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1551,6 +1597,171 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20888F2A-A40C-4759-A75B-3BAAE1BA5F48}">
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="20" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="D3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="B5" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="4">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" t="s">
+        <v>140</v>
+      </c>
+      <c r="J5" s="34">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="B6" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="4">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3">
+        <v>12</v>
+      </c>
+      <c r="F6" s="3">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" t="s">
+        <v>136</v>
+      </c>
+      <c r="I6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="34">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="B7" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" s="4">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3">
+        <v>12</v>
+      </c>
+      <c r="F7" s="3">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I7" t="s">
+        <v>140</v>
+      </c>
+      <c r="J7" s="34">
+        <v>4001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D60CEC-C2FE-4F51-A754-FCEB4D3FF2DF}">
   <dimension ref="A1:AC23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1580,49 +1791,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="20" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
+      <c r="AC1" s="32"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="14" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1631,10 +1842,10 @@
       <c r="F3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="14" t="s">
         <v>77</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -1661,31 +1872,31 @@
       <c r="P3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="Q3" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="R3" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="S3" s="14" t="s">
         <v>93</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U3" s="16" t="s">
+      <c r="U3" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="V3" s="16" t="s">
+      <c r="V3" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="W3" s="14" t="s">
         <v>119</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Y3" s="16" t="s">
+      <c r="Y3" s="14" t="s">
         <v>96</v>
       </c>
       <c r="Z3" s="1" t="s">
@@ -1705,13 +1916,13 @@
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="16">
         <v>46337</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="16">
         <v>46337</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="17" t="s">
         <v>85</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -1746,32 +1957,32 @@
         <f>SUM(M4*I4)</f>
         <v>6000</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="12">
         <v>2.2000000000000002</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4" s="12">
         <f>SUM(N4*O4)</f>
         <v>13200.000000000002</v>
       </c>
-      <c r="Q4" s="21" t="s">
+      <c r="Q4" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="R4" s="22" t="s">
+      <c r="R4" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="S4" s="24" t="s">
+      <c r="S4" s="21" t="s">
         <v>95</v>
       </c>
       <c r="T4" s="5">
         <v>650</v>
       </c>
-      <c r="U4" s="29">
+      <c r="U4" s="25">
         <v>123</v>
       </c>
-      <c r="V4" s="29">
+      <c r="V4" s="25">
         <v>130.1</v>
       </c>
-      <c r="W4" s="29">
+      <c r="W4" s="25">
         <f>SUM(V4-U4)</f>
         <v>7.0999999999999943</v>
       </c>
@@ -1779,20 +1990,20 @@
         <f>SUM(T4*W4)</f>
         <v>4614.9999999999964</v>
       </c>
-      <c r="Y4" s="26" t="s">
+      <c r="Y4" s="23" t="s">
         <v>86</v>
       </c>
       <c r="Z4" s="5">
         <v>35</v>
       </c>
-      <c r="AA4" s="15">
+      <c r="AA4" s="13">
         <f>SUM(Z4*16)</f>
         <v>560</v>
       </c>
       <c r="AB4">
         <v>3</v>
       </c>
-      <c r="AC4" s="15">
+      <c r="AC4" s="13">
         <f>SUM(AA4*AB4)</f>
         <v>1680</v>
       </c>
@@ -1801,25 +2012,25 @@
       <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="16">
         <v>46337</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="16">
         <v>46338</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="18" t="s">
         <v>88</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="15" t="s">
         <v>79</v>
       </c>
       <c r="I5" s="3">
@@ -1842,32 +2053,32 @@
         <f>SUM(M5*I5)</f>
         <v>7500</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="12">
         <v>2.2000000000000002</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5" s="12">
         <f>SUM(N5*O5)</f>
         <v>16500</v>
       </c>
-      <c r="Q5" s="21" t="s">
+      <c r="Q5" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="R5" s="22" t="s">
+      <c r="R5" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="S5" s="24" t="s">
+      <c r="S5" s="21" t="s">
         <v>95</v>
       </c>
       <c r="T5" s="5">
         <v>650</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="25">
         <v>130.1</v>
       </c>
-      <c r="V5" s="29">
+      <c r="V5" s="25">
         <v>142</v>
       </c>
-      <c r="W5" s="29">
+      <c r="W5" s="25">
         <f>SUM(V5-U5)</f>
         <v>11.900000000000006</v>
       </c>
@@ -1875,20 +2086,20 @@
         <f>SUM(T5*W5)</f>
         <v>7735.0000000000036</v>
       </c>
-      <c r="Y5" s="26" t="s">
+      <c r="Y5" s="23" t="s">
         <v>86</v>
       </c>
       <c r="Z5" s="5">
         <v>35</v>
       </c>
-      <c r="AA5" s="15">
+      <c r="AA5" s="13">
         <f>SUM(Z5*16)</f>
         <v>560</v>
       </c>
       <c r="AB5">
         <v>3</v>
       </c>
-      <c r="AC5" s="15">
+      <c r="AC5" s="13">
         <f>SUM(AA5*AB5)</f>
         <v>1680</v>
       </c>
@@ -1897,219 +2108,218 @@
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="16">
         <v>46338</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="16">
         <v>46338</v>
       </c>
       <c r="D6" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="18" t="s">
         <v>89</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="25"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="30"/>
-      <c r="AA6" s="15"/>
-      <c r="AC6" s="15"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="22"/>
+      <c r="V6" s="26"/>
+      <c r="W6" s="26"/>
+      <c r="X6" s="26"/>
+      <c r="AA6" s="13"/>
+      <c r="AC6" s="13"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="25"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="AA7" s="15"/>
-      <c r="AC7" s="15"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="22"/>
+      <c r="V7" s="26"/>
+      <c r="W7" s="26"/>
+      <c r="X7" s="26"/>
+      <c r="AA7" s="13"/>
+      <c r="AC7" s="13"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="25"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="AA8" s="15"/>
-      <c r="AC8" s="15"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="22"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="26"/>
+      <c r="X8" s="26"/>
+      <c r="AA8" s="13"/>
+      <c r="AC8" s="13"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="25"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
-      <c r="AA9" s="15"/>
-      <c r="AC9" s="15"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="22"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="26"/>
+      <c r="AA9" s="13"/>
+      <c r="AC9" s="13"/>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="25"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="AA10" s="15"/>
-      <c r="AC10" s="15"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="22"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="26"/>
+      <c r="X10" s="26"/>
+      <c r="AA10" s="13"/>
+      <c r="AC10" s="13"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="25"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="AA11" s="15"/>
-      <c r="AC11" s="15"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="22"/>
+      <c r="V11" s="26"/>
+      <c r="W11" s="26"/>
+      <c r="X11" s="26"/>
+      <c r="AA11" s="13"/>
+      <c r="AC11" s="13"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="25"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="AA12" s="15"/>
-      <c r="AC12" s="15"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="22"/>
+      <c r="V12" s="26"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="26"/>
+      <c r="AA12" s="13"/>
+      <c r="AC12" s="13"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="25"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="AA13" s="15"/>
-      <c r="AC13" s="15"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="22"/>
+      <c r="V13" s="26"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="26"/>
+      <c r="AA13" s="13"/>
+      <c r="AC13" s="13"/>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="25"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
-      <c r="X14" s="30"/>
-      <c r="AA14" s="15"/>
-      <c r="AC14" s="15"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="22"/>
+      <c r="V14" s="26"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="26"/>
+      <c r="AA14" s="13"/>
+      <c r="AC14" s="13"/>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="25"/>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="AC15" s="15"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="22"/>
+      <c r="V15" s="26"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="26"/>
+      <c r="AC15" s="13"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="25"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30"/>
-      <c r="AC16" s="15"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="22"/>
+      <c r="V16" s="26"/>
+      <c r="W16" s="26"/>
+      <c r="X16" s="26"/>
+      <c r="AC16" s="13"/>
     </row>
     <row r="17" spans="15:29" x14ac:dyDescent="0.35">
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="25"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="AC17" s="15"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="22"/>
+      <c r="V17" s="26"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="26"/>
+      <c r="AC17" s="13"/>
     </row>
     <row r="18" spans="15:29" x14ac:dyDescent="0.35">
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="25"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="AC18" s="15"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="22"/>
+      <c r="V18" s="26"/>
+      <c r="W18" s="26"/>
+      <c r="X18" s="26"/>
+      <c r="AC18" s="13"/>
     </row>
     <row r="19" spans="15:29" x14ac:dyDescent="0.35">
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="25"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="AC19" s="15"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="22"/>
+      <c r="V19" s="26"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="26"/>
+      <c r="AC19" s="13"/>
     </row>
     <row r="20" spans="15:29" x14ac:dyDescent="0.35">
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="25"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="AC20" s="15"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="22"/>
+      <c r="V20" s="26"/>
+      <c r="W20" s="26"/>
+      <c r="X20" s="26"/>
+      <c r="AC20" s="13"/>
     </row>
     <row r="21" spans="15:29" x14ac:dyDescent="0.35">
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="25"/>
-      <c r="V21" s="30"/>
-      <c r="W21" s="30"/>
-      <c r="X21" s="30"/>
-      <c r="AC21" s="15"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="22"/>
+      <c r="V21" s="26"/>
+      <c r="W21" s="26"/>
+      <c r="X21" s="26"/>
+      <c r="AC21" s="13"/>
     </row>
     <row r="22" spans="15:29" x14ac:dyDescent="0.35">
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="23"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="AC22" s="15"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="V22" s="26"/>
+      <c r="W22" s="26"/>
+      <c r="X22" s="26"/>
+      <c r="AC22" s="13"/>
     </row>
     <row r="23" spans="15:29" x14ac:dyDescent="0.35">
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2125,7 +2335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2140,15 +2350,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -2231,7 +2441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E2E9FE-4C9A-413C-89C7-164164E1F1C1}">
   <dimension ref="B2:U10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2242,48 +2452,39 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16" t="s">
+      <c r="Q2" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16" t="s">
+      <c r="S2" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16" t="s">
+      <c r="U2" s="14" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>107</v>
       </c>
       <c r="C3">
@@ -2318,7 +2519,7 @@
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C4" t="s">
@@ -2353,7 +2554,7 @@
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>109</v>
       </c>
       <c r="C5">
@@ -2364,7 +2565,7 @@
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>110</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -2375,76 +2576,76 @@
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="24">
         <v>0.14699999999999999</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="24">
         <v>0.14399999999999999</v>
       </c>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="13">
         <v>400</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15">
+      <c r="D8" s="13"/>
+      <c r="E8" s="13">
         <v>400</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="13">
         <f>SUM(C5*C8)</f>
         <v>44000</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15">
-        <f t="shared" ref="D9:E9" si="0">SUM(E5*E8)</f>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13">
+        <f t="shared" ref="E9" si="0">SUM(E5*E8)</f>
         <v>40000</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="14" t="s">
         <v>114</v>
       </c>
       <c r="C10" t="s">
